--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_2.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_2.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>25.69539713859558</v>
+        <v>119.0576775074005</v>
       </c>
       <c r="D2" t="n">
-        <v>6.480000019073486</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1464085984846641</v>
+        <v>0.4716424528095457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4545454680919647</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3461538553237915</v>
+        <v>0.4210526347160339</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3478260934352875</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3523316085338592</v>
+        <v>0.4067796468734741</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1046586781740188</v>
+        <v>0.1772991418838501</v>
       </c>
       <c r="K2" t="n">
-        <v>13.49935221672058</v>
+        <v>54.55048298835754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0382686614990234</v>
+        <v>0.0791281414031982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0794192457199096</v>
+        <v>0.4746424770355225</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08376228809356689</v>
+        <v>0.1725244617462158</v>
       </c>
       <c r="O2" t="n">
-        <v>1.913433074951172</v>
+        <v>3.956407070159912</v>
       </c>
       <c r="P2" t="n">
-        <v>3.970962285995483</v>
+        <v>23.73212385177612</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.188114404678345</v>
+        <v>8.626223087310791</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-153630</t>
+          <t>20250725-214004</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>44.75134325027466</v>
+        <v>63.51629018783569</v>
       </c>
       <c r="D3" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1466281441626725</v>
+        <v>0.4706346505674822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3333333432674408</v>
+        <v>0.2857142984867096</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4188034236431122</v>
+        <v>0.3776824176311493</v>
       </c>
       <c r="H3" t="n">
-        <v>0.270676702260971</v>
+        <v>0.380952388048172</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2835820913314819</v>
+        <v>0.3771929740905761</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1081664115190506</v>
+        <v>0.1766112446784973</v>
       </c>
       <c r="K3" t="n">
-        <v>13.43258690834045</v>
+        <v>54.46943497657776</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373887300491333</v>
+        <v>0.0797787523269653</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0773399543762207</v>
+        <v>0.4627832078933716</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0860144567489624</v>
+        <v>0.1694988441467285</v>
       </c>
       <c r="O3" t="n">
-        <v>1.869436502456665</v>
+        <v>3.988937616348267</v>
       </c>
       <c r="P3" t="n">
-        <v>3.866997718811035</v>
+        <v>23.13916039466858</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.30072283744812</v>
+        <v>8.474942207336426</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-153748</t>
+          <t>20250725-214421</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>25.30725908279419</v>
+        <v>54.07285404205322</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1473251129018849</v>
+        <v>0.4717072000106175</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.2105263173580169</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4100418388843536</v>
+        <v>0.2775510251522064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3687150776386261</v>
+        <v>0.2268041223287582</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3387978076934814</v>
+        <v>0.2448979616165161</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0897835716605186</v>
+        <v>0.1772573143243789</v>
       </c>
       <c r="K4" t="n">
-        <v>13.56775760650635</v>
+        <v>53.94293403625488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0392326593399047</v>
+        <v>0.08287449836730949</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0769330167770385</v>
+        <v>0.4609525442123413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0853833246231079</v>
+        <v>0.1640223836898803</v>
       </c>
       <c r="O4" t="n">
-        <v>1.96163296699524</v>
+        <v>4.143724918365479</v>
       </c>
       <c r="P4" t="n">
-        <v>3.846650838851929</v>
+        <v>23.04762721061707</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.269166231155396</v>
+        <v>8.201119184494019</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-153926</t>
+          <t>20250725-214733</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -959,56 +959,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>25.28828096389771</v>
+        <v>52.59506416320801</v>
       </c>
       <c r="D5" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1463801372667838</v>
+        <v>0.4715082409481207</v>
       </c>
       <c r="F5" t="n">
         <v>0.3333333432674408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2309859097003936</v>
+        <v>0.3076923191547394</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1678321659564972</v>
+        <v>0.1791044771671295</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1666666716337204</v>
+        <v>0.1428571492433548</v>
       </c>
       <c r="J5" t="n">
-        <v>0.091007225215435</v>
+        <v>0.1795278787612915</v>
       </c>
       <c r="K5" t="n">
-        <v>13.36837005615234</v>
+        <v>54.54519510269165</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0349518728256225</v>
+        <v>0.0812764549255371</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06847220897674559</v>
+        <v>0.4585528564453125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0865973091125488</v>
+        <v>0.1710151767730713</v>
       </c>
       <c r="O5" t="n">
-        <v>1.747593641281128</v>
+        <v>4.063822746276856</v>
       </c>
       <c r="P5" t="n">
-        <v>3.42361044883728</v>
+        <v>22.92764282226562</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.329865455627441</v>
+        <v>8.550758838653564</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-154044</t>
+          <t>20250725-215044</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>29.03203344345093</v>
+        <v>53.2286696434021</v>
       </c>
       <c r="D6" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1417459674617823</v>
+        <v>0.47019262611866</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3138461410999298</v>
+        <v>0.3700440526008606</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3020833432674408</v>
+        <v>0.3606557250022888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3253588378429413</v>
+        <v>0.3555555641651153</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1049238294363021</v>
+        <v>0.1778254508972168</v>
       </c>
       <c r="K6" t="n">
-        <v>13.37768578529358</v>
+        <v>54.8253710269928</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0351402568817138</v>
+        <v>0.08452177524566649</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06880935192108149</v>
+        <v>0.463649091720581</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0847022199630737</v>
+        <v>0.1652322769165039</v>
       </c>
       <c r="O6" t="n">
-        <v>1.757012844085693</v>
+        <v>4.226088762283325</v>
       </c>
       <c r="P6" t="n">
-        <v>3.440467596054077</v>
+        <v>23.18245458602905</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.235110998153687</v>
+        <v>8.261613845825195</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-154206</t>
+          <t>20250725-215344</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>106.1250655651092</v>
+        <v>219.8191528320312</v>
       </c>
       <c r="D2" t="n">
-        <v>9.829999923706056</v>
+        <v>20.71999931335449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.290238247718662</v>
+        <v>0.5443300619721413</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5454545617103577</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3783783912658691</v>
+        <v>0.5729729533195496</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3835616409778595</v>
+        <v>0.5744680762290955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3979591727256775</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1286363303661346</v>
+        <v>0.1316677331924438</v>
       </c>
       <c r="K2" t="n">
-        <v>54.4113347530365</v>
+        <v>74.45181751251221</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08145006656646719</v>
+        <v>0.0694700145721435</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4541518402099609</v>
+        <v>0.1995874309539795</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1723076915740966</v>
+        <v>0.1965523147583008</v>
       </c>
       <c r="O2" t="n">
-        <v>4.072503328323364</v>
+        <v>3.473500728607178</v>
       </c>
       <c r="P2" t="n">
-        <v>22.70759201049805</v>
+        <v>9.979371547698976</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.615384578704834</v>
+        <v>9.827615737915041</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-050550</t>
+          <t>20250724-132052</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>60.28466463088989</v>
+        <v>299.8575420379639</v>
       </c>
       <c r="D3" t="n">
-        <v>9.779999732971191</v>
+        <v>20.64999961853028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2887938993099408</v>
+        <v>0.5196092408823679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3652968108654022</v>
+        <v>0.5205479264259338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3614457845687866</v>
+        <v>0.5111111402511597</v>
       </c>
       <c r="I3" t="n">
-        <v>0.349397599697113</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1314731240272522</v>
+        <v>0.1454273760318756</v>
       </c>
       <c r="K3" t="n">
-        <v>54.52354955673218</v>
+        <v>81.33710861206055</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08749507904052729</v>
+        <v>0.0745327997207641</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4540836095809936</v>
+        <v>0.2048588466644287</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1758099269866943</v>
+        <v>0.1926486253738403</v>
       </c>
       <c r="O3" t="n">
-        <v>4.374753952026367</v>
+        <v>3.726639986038208</v>
       </c>
       <c r="P3" t="n">
-        <v>22.70418047904968</v>
+        <v>10.24294233322144</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.790496349334717</v>
+        <v>9.632431268692017</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-050957</t>
+          <t>20250724-132722</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>83.49179315567017</v>
+        <v>251.3041813373566</v>
       </c>
       <c r="D4" t="n">
-        <v>9.810000419616699</v>
+        <v>21.18000030517578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2896719660077776</v>
+        <v>0.5163271651751753</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4114832580089569</v>
+        <v>0.4455958604812622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4210526347160339</v>
+        <v>0.4387755095958709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4226804077625274</v>
+        <v>0.1612903177738189</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1297062337398529</v>
+        <v>0.1458564698696136</v>
       </c>
       <c r="K4" t="n">
-        <v>55.07289147377014</v>
+        <v>74.50025653839111</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09111157417297359</v>
+        <v>0.06972481250762939</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4582533359527588</v>
+        <v>0.1980284690856933</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1728773164749145</v>
+        <v>0.1863114595413208</v>
       </c>
       <c r="O4" t="n">
-        <v>4.555578708648682</v>
+        <v>3.48624062538147</v>
       </c>
       <c r="P4" t="n">
-        <v>22.91266679763794</v>
+        <v>9.901423454284668</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.643865823745728</v>
+        <v>9.31557297706604</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-051317</t>
+          <t>20250724-133512</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>56.35900115966797</v>
+        <v>270.912656545639</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779999732971191</v>
+        <v>19.48999977111816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.289797050111434</v>
+        <v>0.544047615012607</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3846153914928436</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4137931168079376</v>
+        <v>0.4550264477729797</v>
       </c>
       <c r="H5" t="n">
-        <v>0.410256415605545</v>
+        <v>0.455089807510376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4183673560619354</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1273781359195709</v>
+        <v>0.140995591878891</v>
       </c>
       <c r="K5" t="n">
-        <v>55.05384349822998</v>
+        <v>80.73674964904785</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0839579772949218</v>
+        <v>0.0712111377716064</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4616830015182495</v>
+        <v>0.1985132122039795</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1729549503326416</v>
+        <v>0.1950371170043945</v>
       </c>
       <c r="O5" t="n">
-        <v>4.197898864746094</v>
+        <v>3.560556888580322</v>
       </c>
       <c r="P5" t="n">
-        <v>23.08415007591248</v>
+        <v>9.925660610198976</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.64774751663208</v>
+        <v>9.751855850219728</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-051702</t>
+          <t>20250724-134213</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>41.51093912124634</v>
+        <v>246.3330373764038</v>
       </c>
       <c r="D6" t="n">
-        <v>9.739999771118164</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2904042800267537</v>
+        <v>0.5333356781681972</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4615384638309479</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3508771955966949</v>
+        <v>0.5654450058937073</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1940298527479171</v>
+        <v>0.5699999928474426</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2173912972211837</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1286516338586807</v>
+        <v>0.1299226731061935</v>
       </c>
       <c r="K6" t="n">
-        <v>57.82150173187256</v>
+        <v>74.72168874740601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0855242252349853</v>
+        <v>0.06852159023284909</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4541436433792114</v>
+        <v>0.2006327486038208</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1701936769485473</v>
+        <v>0.1864763355255126</v>
       </c>
       <c r="O6" t="n">
-        <v>4.276211261749268</v>
+        <v>3.426079511642456</v>
       </c>
       <c r="P6" t="n">
-        <v>22.70718216896057</v>
+        <v>10.03163743019104</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.509683847427368</v>
+        <v>9.323816776275637</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-052008</t>
+          <t>20250724-134933</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>223.2138428688049</v>
+        <v>191.7470998764038</v>
       </c>
       <c r="D2" t="n">
-        <v>14.22999954223633</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4859807406152998</v>
+        <v>0.3156822808817321</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4761904776096344</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5649717450141907</v>
+        <v>0.4069767296314239</v>
       </c>
       <c r="H2" t="n">
-        <v>0.464516133069992</v>
+        <v>0.3625000119209289</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.3229813575744629</v>
       </c>
       <c r="J2" t="n">
-        <v>0.132943108677864</v>
+        <v>0.161775067448616</v>
       </c>
       <c r="K2" t="n">
-        <v>80.91721224784851</v>
+        <v>50.77402257919312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0724073266983032</v>
+        <v>0.0719792032241821</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1970185232162475</v>
+        <v>0.2252379035949707</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1879352474212646</v>
+        <v>0.1755965518951416</v>
       </c>
       <c r="O2" t="n">
-        <v>3.620366334915161</v>
+        <v>3.598960161209106</v>
       </c>
       <c r="P2" t="n">
-        <v>9.850926160812378</v>
+        <v>11.26189517974854</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.396762371063232</v>
+        <v>8.77982759475708</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-103035</t>
+          <t>20250726-231338</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>251.7218928337097</v>
+        <v>180.6511116027832</v>
       </c>
       <c r="D3" t="n">
-        <v>14.61999988555908</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4646301997058532</v>
+        <v>0.3045973125431273</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.5925925970077515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5945945978164673</v>
+        <v>0.5197740197181702</v>
       </c>
       <c r="H3" t="n">
-        <v>0.584269642829895</v>
+        <v>0.5076141953468323</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.4932735562324524</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1362682878971099</v>
+        <v>0.1600533723831176</v>
       </c>
       <c r="K3" t="n">
-        <v>74.61786103248596</v>
+        <v>50.83925342559815</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0745391941070556</v>
+        <v>0.0786791944503784</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1972477102279663</v>
+        <v>0.2206926918029785</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2034154605865478</v>
+        <v>0.18177743434906</v>
       </c>
       <c r="O3" t="n">
-        <v>3.726959705352783</v>
+        <v>3.933959722518921</v>
       </c>
       <c r="P3" t="n">
-        <v>9.862385511398315</v>
+        <v>11.03463459014893</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.17077302932739</v>
+        <v>9.088871717453005</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-103708</t>
+          <t>20250726-231906</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>207.6997816562653</v>
+        <v>274.8327915668488</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22000026702881</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.464358618198815</v>
+        <v>0.3077328725599906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.3529411852359772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5418719053268433</v>
+        <v>0.4334975481033325</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5586591958999634</v>
+        <v>0.3401360511779785</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1034482792019844</v>
+        <v>0.3235294222831726</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1263671815395355</v>
+        <v>0.162100464105606</v>
       </c>
       <c r="K4" t="n">
-        <v>74.98524689674377</v>
+        <v>51.26197600364685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0735776376724243</v>
+        <v>0.07259949684143061</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1976989126205444</v>
+        <v>0.2262684202194214</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1906717443466186</v>
+        <v>0.186679573059082</v>
       </c>
       <c r="O4" t="n">
-        <v>3.678881883621216</v>
+        <v>3.629974842071533</v>
       </c>
       <c r="P4" t="n">
-        <v>9.884945631027222</v>
+        <v>11.31342101097107</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.533587217330933</v>
+        <v>9.333978652954102</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-104401</t>
+          <t>20250726-232422</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>207.5668470859528</v>
+        <v>212.7670359611511</v>
       </c>
       <c r="D5" t="n">
-        <v>14.25</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4773622074369656</v>
+        <v>0.3132472055138282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5333333611488342</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5978260636329651</v>
+        <v>0.3695652186870575</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4556961953639984</v>
+        <v>0.365714281797409</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3926380276679992</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1304117441177368</v>
+        <v>0.1627774089574813</v>
       </c>
       <c r="K5" t="n">
-        <v>74.77440714836121</v>
+        <v>52.12433004379272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0728496599197387</v>
+        <v>0.0717730283737182</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1970729494094848</v>
+        <v>0.2239615392684936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2005327320098877</v>
+        <v>0.1744021415710449</v>
       </c>
       <c r="O5" t="n">
-        <v>3.642482995986938</v>
+        <v>3.588651418685913</v>
       </c>
       <c r="P5" t="n">
-        <v>9.853647470474243</v>
+        <v>11.19807696342468</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.02663660049438</v>
+        <v>8.720107078552246</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-105018</t>
+          <t>20250726-233103</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>204.7893056869507</v>
+        <v>197.4035108089447</v>
       </c>
       <c r="D6" t="n">
-        <v>14.52999973297119</v>
+        <v>10.09000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4715668655047982</v>
+        <v>0.3080999193326482</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4166666567325592</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4591836631298065</v>
+        <v>0.4629629552364349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4712041914463043</v>
+        <v>0.4352941215038299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4766839444637298</v>
+        <v>0.2695035338401794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1349474489688873</v>
+        <v>0.1636885702610016</v>
       </c>
       <c r="K6" t="n">
-        <v>81.04907655715942</v>
+        <v>45.21664905548096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0753896808624267</v>
+        <v>0.0715385818481445</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1990481519699096</v>
+        <v>0.2269818305969238</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2060337162017822</v>
+        <v>0.1748222303390502</v>
       </c>
       <c r="O6" t="n">
-        <v>3.769484043121338</v>
+        <v>3.576929092407227</v>
       </c>
       <c r="P6" t="n">
-        <v>9.952407598495483</v>
+        <v>11.34909152984619</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.30168581008911</v>
+        <v>8.741111516952515</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-105626</t>
+          <t>20250726-233653</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>170.3910024166107</v>
+        <v>84.03934693336487</v>
       </c>
       <c r="D2" t="n">
-        <v>9.460000038146973</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2947974593140358</v>
+        <v>0.1541165046926055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3157894611358642</v>
+        <v>0.2857142984867096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.1219512224197387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.1202185824513435</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2255639135837555</v>
+        <v>0.0467836260795593</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1383578032255172</v>
+        <v>0.0893448069691658</v>
       </c>
       <c r="K2" t="n">
-        <v>51.76376557350159</v>
+        <v>24.64430499076844</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0848357009887695</v>
+        <v>0.0458555746078491</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2209417152404785</v>
+        <v>0.07880424022674561</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1817602634429931</v>
+        <v>0.0840237998962402</v>
       </c>
       <c r="O2" t="n">
-        <v>4.241785049438477</v>
+        <v>2.292778730392456</v>
       </c>
       <c r="P2" t="n">
-        <v>11.04708576202393</v>
+        <v>3.94021201133728</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.088013172149658</v>
+        <v>4.201189994812012</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-004644</t>
+          <t>20250728-040200</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
-        <v>192.9125959873199</v>
+        <v>91.08051133155824</v>
       </c>
       <c r="D3" t="n">
-        <v>9.060000419616699</v>
+        <v>5.230000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2812506066901343</v>
+        <v>0.1496166948412285</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.4444444477558136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2592592537403106</v>
+        <v>0.3272727131843567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2278480976819992</v>
+        <v>0.365714281797409</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2147651016712188</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1404211968183517</v>
+        <v>0.08670101314783089</v>
       </c>
       <c r="K3" t="n">
-        <v>45.43249154090881</v>
+        <v>18.88932275772095</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08865457534790031</v>
+        <v>0.045033254623413</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2197980880737304</v>
+        <v>0.0801600933074951</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1733474159240722</v>
+        <v>0.08265283107757559</v>
       </c>
       <c r="O3" t="n">
-        <v>4.43272876739502</v>
+        <v>2.251662731170654</v>
       </c>
       <c r="P3" t="n">
-        <v>10.98990440368652</v>
+        <v>4.008004665374756</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.667370796203613</v>
+        <v>4.132641553878784</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-005153</t>
+          <t>20250728-040442</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>150.3633921146393</v>
+        <v>72.89150619506836</v>
       </c>
       <c r="D4" t="n">
-        <v>9.210000038146973</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2841077613276104</v>
+        <v>0.1506028677458348</v>
       </c>
       <c r="F4" t="n">
-        <v>0.375</v>
+        <v>0.4615384638309479</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1333333402872085</v>
+        <v>0.3402061760425567</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1438848972320556</v>
+        <v>0.2388059645891189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09448818862438201</v>
+        <v>0.3055555522441864</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1441719979047775</v>
+        <v>0.0872630104422569</v>
       </c>
       <c r="K4" t="n">
-        <v>51.4896764755249</v>
+        <v>24.43006300926208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0872767639160156</v>
+        <v>0.0443921136856079</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2193724489212036</v>
+        <v>0.0802421379089355</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1862553071975708</v>
+        <v>0.09217468738555901</v>
       </c>
       <c r="O4" t="n">
-        <v>4.363838195800781</v>
+        <v>2.219605684280396</v>
       </c>
       <c r="P4" t="n">
-        <v>10.96862244606018</v>
+        <v>4.012106895446777</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.31276535987854</v>
+        <v>4.608734369277954</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-005723</t>
+          <t>20250728-040731</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="n">
-        <v>207.8695192337036</v>
+        <v>83.32446932792664</v>
       </c>
       <c r="D5" t="n">
-        <v>8.989999771118164</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.288490379065798</v>
+        <v>0.1500272136181592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4545454680919647</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2477341443300247</v>
+        <v>0.1489361673593521</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2509505748748779</v>
+        <v>0.1428571492433548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.252427190542221</v>
+        <v>0.1614906787872314</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1444644331932068</v>
+        <v>0.0786544606089592</v>
       </c>
       <c r="K5" t="n">
-        <v>45.42087817192078</v>
+        <v>24.13805341720581</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0828556108474731</v>
+        <v>0.046280026435852</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2258114099502563</v>
+        <v>0.0782097482681274</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1736383628845214</v>
+        <v>0.0848344230651855</v>
       </c>
       <c r="O5" t="n">
-        <v>4.142780542373657</v>
+        <v>2.314001321792603</v>
       </c>
       <c r="P5" t="n">
-        <v>11.29057049751282</v>
+        <v>3.910487413406372</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.681918144226074</v>
+        <v>4.241721153259277</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-010201</t>
+          <t>20250728-041003</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>179.5778467655182</v>
+        <v>91.47480630874634</v>
       </c>
       <c r="D6" t="n">
-        <v>9.210000038146973</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2845708868082832</v>
+        <v>0.1468708154003498</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5333333611488342</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2891566157341003</v>
+        <v>0.3720930218696594</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2535211145877838</v>
+        <v>0.2896551787853241</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2133333384990692</v>
+        <v>0.1705426424741745</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1425768435001373</v>
+        <v>0.0915511697530746</v>
       </c>
       <c r="K6" t="n">
-        <v>50.78408598899841</v>
+        <v>24.93053674697876</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0880550146102905</v>
+        <v>0.0442311286926269</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2196282386779785</v>
+        <v>0.0786827898025512</v>
       </c>
       <c r="N6" t="n">
-        <v>0.182054214477539</v>
+        <v>0.0824192476272583</v>
       </c>
       <c r="O6" t="n">
-        <v>4.402750730514526</v>
+        <v>2.211556434631348</v>
       </c>
       <c r="P6" t="n">
-        <v>10.98141193389893</v>
+        <v>3.934139490127564</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.102710723876951</v>
+        <v>4.120962381362915</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-010741</t>
+          <t>20250728-041244</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>73.80639457702637</v>
+        <v>121.0203001499176</v>
       </c>
       <c r="D2" t="n">
-        <v>3.230000019073486</v>
+        <v>8.149999618530273</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1641864851117133</v>
+        <v>0.2488393326816351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="G2" t="n">
-        <v>0.199004977941513</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1931818127632141</v>
+        <v>0.3225806355476379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112676054239273</v>
+        <v>0.3499999940395355</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09322544932365411</v>
+        <v>0.1291291564702987</v>
       </c>
       <c r="K2" t="n">
-        <v>24.16841149330139</v>
+        <v>38.81032729148865</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0506724500656127</v>
+        <v>0.0667530584335327</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07907998085021969</v>
+        <v>0.1372266769409179</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09097547054290769</v>
+        <v>0.1477493190765381</v>
       </c>
       <c r="O2" t="n">
-        <v>2.53362250328064</v>
+        <v>3.337652921676636</v>
       </c>
       <c r="P2" t="n">
-        <v>3.953999042510985</v>
+        <v>6.861333847045898</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.548773527145386</v>
+        <v>7.387465953826904</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-162009</t>
+          <t>20250729-071129</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>68.4286687374115</v>
+        <v>127.229551076889</v>
       </c>
       <c r="D3" t="n">
-        <v>3.119999885559082</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1647878185261127</v>
+        <v>0.2389845254902656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.375</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1690140813589096</v>
+        <v>0.4108107984066009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1333333402872085</v>
+        <v>0.328947365283966</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0327868834137916</v>
+        <v>0.3098591566085815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0875359028577804</v>
+        <v>0.1197438240051269</v>
       </c>
       <c r="K3" t="n">
-        <v>24.14433264732361</v>
+        <v>39.11809849739075</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0569271945953369</v>
+        <v>0.0569881629943847</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0794682455062866</v>
+        <v>0.1389499473571777</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08485385417938229</v>
+        <v>0.1398672246932983</v>
       </c>
       <c r="O3" t="n">
-        <v>2.846359729766846</v>
+        <v>2.849408149719238</v>
       </c>
       <c r="P3" t="n">
-        <v>3.973412275314331</v>
+        <v>6.947497367858887</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.242692708969116</v>
+        <v>6.993361234664917</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-162242</t>
+          <t>20250729-071518</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>73.96714401245117</v>
+        <v>138.8308527469635</v>
       </c>
       <c r="D4" t="n">
-        <v>3.269999980926514</v>
+        <v>7.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1626349045170677</v>
+        <v>0.2380791991949081</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2872928082942962</v>
+        <v>0.4205128252506256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1884057968854904</v>
+        <v>0.4183673560619354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1374045759439468</v>
+        <v>0.3258427083492279</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0977643504738807</v>
+        <v>0.1186602413654327</v>
       </c>
       <c r="K4" t="n">
-        <v>24.62382555007935</v>
+        <v>33.09755396842957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.050465235710144</v>
+        <v>0.0568164682388305</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0793024492263794</v>
+        <v>0.1393020009994506</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0937081241607666</v>
+        <v>0.1536509799957275</v>
       </c>
       <c r="O4" t="n">
-        <v>2.523261785507202</v>
+        <v>2.840823411941528</v>
       </c>
       <c r="P4" t="n">
-        <v>3.96512246131897</v>
+        <v>6.965100049972534</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.68540620803833</v>
+        <v>7.682548999786377</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-162509</t>
+          <t>20250729-071913</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>75.07976675033569</v>
+        <v>124.64905834198</v>
       </c>
       <c r="D5" t="n">
-        <v>3.019999980926514</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1640758659950522</v>
+        <v>0.2497164153931092</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3076923191547394</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2028985470533371</v>
+        <v>0.4042553305625915</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2095238119363784</v>
+        <v>0.3832335472106933</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2215189933776855</v>
+        <v>0.275132268667221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0922237113118171</v>
+        <v>0.1150227040052414</v>
       </c>
       <c r="K5" t="n">
-        <v>24.72176742553711</v>
+        <v>39.18929100036621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0521596622467041</v>
+        <v>0.0579476070404052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0786313819885253</v>
+        <v>0.1449614334106445</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08437424182891839</v>
+        <v>0.1515286922454834</v>
       </c>
       <c r="O5" t="n">
-        <v>2.607983112335205</v>
+        <v>2.897380352020264</v>
       </c>
       <c r="P5" t="n">
-        <v>3.93156909942627</v>
+        <v>7.248071670532227</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.218712091445923</v>
+        <v>7.57643461227417</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-162743</t>
+          <t>20250729-072310</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>92.37391400337221</v>
+        <v>150.0197603702545</v>
       </c>
       <c r="D6" t="n">
-        <v>3.160000085830688</v>
+        <v>7.340000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.159664205529473</v>
+        <v>0.2392048533000643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3571428656578064</v>
+        <v>0.4166666567325592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3170731663703918</v>
+        <v>0.4588744640350342</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3439490497112274</v>
+        <v>0.4792626798152923</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3214285671710968</v>
+        <v>0.4553571343421936</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08384121954441071</v>
+        <v>0.1217717230319976</v>
       </c>
       <c r="K6" t="n">
-        <v>24.63376355171204</v>
+        <v>39.04856395721436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0505139064788818</v>
+        <v>0.0563250589370727</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07898795127868651</v>
+        <v>0.1397321796417236</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0847703170776367</v>
+        <v>0.1403260612487793</v>
       </c>
       <c r="O6" t="n">
-        <v>2.525695323944092</v>
+        <v>2.816252946853638</v>
       </c>
       <c r="P6" t="n">
-        <v>3.949397563934326</v>
+        <v>6.986608982086182</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.238515853881836</v>
+        <v>7.016303062438965</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-163018</t>
+          <t>20250729-072703</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>128.9108815193176</v>
+        <v>39.40352749824524</v>
       </c>
       <c r="D2" t="n">
-        <v>7.03000020980835</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2483301519726713</v>
+        <v>0.1358368269034794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.1818181872367859</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3258427083492279</v>
+        <v>0.2236842066049575</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3265306055545807</v>
+        <v>0.0517241396009922</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2399999946355819</v>
+        <v>0.0517241396009922</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1164459511637687</v>
+        <v>0.0988865792751312</v>
       </c>
       <c r="K2" t="n">
-        <v>39.28195667266846</v>
+        <v>13.96977281570435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0737644481658935</v>
+        <v>0.0340760326385498</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1386265325546264</v>
+        <v>0.047233772277832</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1436971855163574</v>
+        <v>0.0404210710525512</v>
       </c>
       <c r="O2" t="n">
-        <v>3.688222408294678</v>
+        <v>1.70380163192749</v>
       </c>
       <c r="P2" t="n">
-        <v>6.931326627731323</v>
+        <v>2.361688613891602</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.184859275817871</v>
+        <v>2.021053552627563</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-040608</t>
+          <t>20250730-081957</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>116.0818431377411</v>
+        <v>42.32495188713074</v>
       </c>
       <c r="D3" t="n">
-        <v>5.96999979019165</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2475328356027603</v>
+        <v>0.1365082194959675</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3255814015865326</v>
+        <v>0.1666666716337204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4074074029922485</v>
+        <v>0.1546391695737838</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4311926662921905</v>
+        <v>0.0981595069169998</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2647058963775635</v>
+        <v>0.0880503132939338</v>
       </c>
       <c r="J3" t="n">
-        <v>0.114830233156681</v>
+        <v>0.0934007540345192</v>
       </c>
       <c r="K3" t="n">
-        <v>39.57192802429199</v>
+        <v>13.87268662452698</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0716548776626587</v>
+        <v>0.0458725500106811</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1436411476135254</v>
+        <v>0.0473058080673217</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1416694116592407</v>
+        <v>0.041284852027893</v>
       </c>
       <c r="O3" t="n">
-        <v>3.582743883132935</v>
+        <v>2.293627500534058</v>
       </c>
       <c r="P3" t="n">
-        <v>7.18205738067627</v>
+        <v>2.365290403366089</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.083470582962036</v>
+        <v>2.064242601394653</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-041007</t>
+          <t>20250730-082131</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>112.4441170692444</v>
+        <v>64.88586115837097</v>
       </c>
       <c r="D4" t="n">
-        <v>6.679999828338623</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2429582717066461</v>
+        <v>0.1363130579037325</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3000000119209289</v>
+        <v>0.375</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2015503942966461</v>
+        <v>0.3192488253116607</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1794871836900711</v>
+        <v>0.3192488253116607</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1194029822945594</v>
+        <v>0.3188405930995941</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1122672483325004</v>
+        <v>0.1060053408145904</v>
       </c>
       <c r="K4" t="n">
-        <v>39.49464201927185</v>
+        <v>13.74014258384705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0731180429458618</v>
+        <v>0.0383910131454467</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1398568296432495</v>
+        <v>0.0495692300796508</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1415688800811767</v>
+        <v>0.0419758367538452</v>
       </c>
       <c r="O4" t="n">
-        <v>3.655902147293091</v>
+        <v>1.919550657272339</v>
       </c>
       <c r="P4" t="n">
-        <v>6.992841482162476</v>
+        <v>2.478461503982544</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.078444004058838</v>
+        <v>2.098791837692261</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-041354</t>
+          <t>20250730-082307</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>125.7968270778656</v>
+        <v>32.4524073600769</v>
       </c>
       <c r="D5" t="n">
-        <v>5.980000019073486</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2467102324185164</v>
+        <v>0.1356569811319693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2051282078027725</v>
+        <v>0.2857142984867096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3797468245029449</v>
+        <v>0.0669642835855484</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3744680881500244</v>
+        <v>0.0128205129876732</v>
       </c>
       <c r="I5" t="n">
-        <v>0.260869562625885</v>
+        <v>0.0128205129876732</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1194325610995292</v>
+        <v>0.0912168100476265</v>
       </c>
       <c r="K5" t="n">
-        <v>39.05403780937195</v>
+        <v>13.91878485679626</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07065926551818839</v>
+        <v>0.0450291395187377</v>
       </c>
       <c r="M5" t="n">
-        <v>0.139798617362976</v>
+        <v>0.0474859857559204</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1439390039443969</v>
+        <v>0.043323106765747</v>
       </c>
       <c r="O5" t="n">
-        <v>3.532963275909424</v>
+        <v>2.25145697593689</v>
       </c>
       <c r="P5" t="n">
-        <v>6.989930868148804</v>
+        <v>2.374299287796021</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.196950197219849</v>
+        <v>2.166155338287353</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-041737</t>
+          <t>20250730-082506</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>129.937908411026</v>
+        <v>47.00822639465332</v>
       </c>
       <c r="D6" t="n">
-        <v>6.440000057220459</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.245045919281741</v>
+        <v>0.1357864520307314</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3199999928474426</v>
+        <v>0.2105263173580169</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1877934336662292</v>
+        <v>0.1563785970211029</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1818181872367859</v>
+        <v>0.1546391695737838</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1714285761117935</v>
+        <v>0.1397849470376968</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1150657162070274</v>
+        <v>0.084816426038742</v>
       </c>
       <c r="K6" t="n">
-        <v>39.79987192153931</v>
+        <v>13.9785726070404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06589759349822991</v>
+        <v>0.0306206941604614</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1396598243713379</v>
+        <v>0.047576675415039</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1425853109359741</v>
+        <v>0.0438746213912963</v>
       </c>
       <c r="O6" t="n">
-        <v>3.294879674911499</v>
+        <v>1.531034708023071</v>
       </c>
       <c r="P6" t="n">
-        <v>6.982991218566895</v>
+        <v>2.378833770751953</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.129265546798706</v>
+        <v>2.19373106956482</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-042132</t>
+          <t>20250730-082633</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="C2" t="n">
-        <v>37.50004315376282</v>
+        <v>81.19156169891357</v>
       </c>
       <c r="D2" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1050886741402197</v>
+        <v>0.2365894621308845</v>
       </c>
       <c r="F2" t="n">
         <v>0.3076923191547394</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2590673565864563</v>
+        <v>0.27947598695755</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2307692319154739</v>
+        <v>0.2634730637073517</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2266666740179062</v>
+        <v>0.2738095223903656</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0778075903654098</v>
+        <v>0.09357220679521561</v>
       </c>
       <c r="K2" t="n">
-        <v>9.544999361038208</v>
+        <v>29.43707394599915</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0459427833557128</v>
+        <v>0.0449192285537719</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0454104471206665</v>
+        <v>0.1233671569824218</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06394800186157221</v>
+        <v>0.0899696493148803</v>
       </c>
       <c r="O2" t="n">
-        <v>2.297139167785645</v>
+        <v>2.245961427688598</v>
       </c>
       <c r="P2" t="n">
-        <v>2.270522356033325</v>
+        <v>6.168357849121094</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.197400093078613</v>
+        <v>4.498482465744019</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-180616</t>
+          <t>20250731-010115</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7659,53 +7659,53 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>45.36940288543701</v>
+        <v>63.37375640869141</v>
       </c>
       <c r="D3" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1101259498272911</v>
+        <v>0.2379336448039038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4248704612255096</v>
+        <v>0.4204545319080353</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4304932653903961</v>
+        <v>0.387499988079071</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4266666769981384</v>
+        <v>0.3756345212459564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08363133668899531</v>
+        <v>0.0962298512458801</v>
       </c>
       <c r="K3" t="n">
-        <v>14.80393075942993</v>
+        <v>29.26555800437927</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0426624345779418</v>
+        <v>0.0414509773254394</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0521679925918579</v>
+        <v>0.1309232187271118</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0575768184661865</v>
+        <v>0.09247066974639891</v>
       </c>
       <c r="O3" t="n">
-        <v>2.133121728897095</v>
+        <v>2.072548866271973</v>
       </c>
       <c r="P3" t="n">
-        <v>2.608399629592896</v>
+        <v>6.546160936355591</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.878840923309326</v>
+        <v>4.623533487319946</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-180752</t>
+          <t>20250731-010401</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>58.21130180358887</v>
+        <v>49.80793523788452</v>
       </c>
       <c r="D4" t="n">
-        <v>1.730000019073486</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.107912309845037</v>
+        <v>0.2374327697537162</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2580645084381103</v>
+        <v>0.3529411852359772</v>
       </c>
       <c r="G4" t="n">
-        <v>0.125</v>
+        <v>0.2636363506317138</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0625</v>
+        <v>0.2569832503795624</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0495867766439914</v>
+        <v>0.2790697813034057</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0871911346912384</v>
+        <v>0.1037724241614341</v>
       </c>
       <c r="K4" t="n">
-        <v>14.84439039230347</v>
+        <v>29.14271378517151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0400602912902832</v>
+        <v>0.0428448772430419</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0508607530593872</v>
+        <v>0.1308697080612182</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0569802618026733</v>
+        <v>0.0905489349365234</v>
       </c>
       <c r="O4" t="n">
-        <v>2.00301456451416</v>
+        <v>2.1422438621521</v>
       </c>
       <c r="P4" t="n">
-        <v>2.54303765296936</v>
+        <v>6.543485403060913</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.849013090133667</v>
+        <v>4.527446746826172</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-180935</t>
+          <t>20250731-010630</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7898,56 +7898,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>87.24979496002197</v>
+        <v>49.23348116874695</v>
       </c>
       <c r="D5" t="n">
-        <v>1.730000019073486</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1108011788054674</v>
+        <v>0.2367886613038453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3478260934352875</v>
+        <v>0.2857142984867096</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4266666769981384</v>
+        <v>0.1893491148948669</v>
       </c>
       <c r="H5" t="n">
-        <v>0.427807480096817</v>
+        <v>0.1826484054327011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4153005480766296</v>
+        <v>0.1728395074605941</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0707604438066482</v>
+        <v>0.1016173139214515</v>
       </c>
       <c r="K5" t="n">
-        <v>15.15977478027344</v>
+        <v>24.022127866745</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0410677242279052</v>
+        <v>0.0453310823440551</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0454000854492187</v>
+        <v>0.1239622640609741</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0577376270294189</v>
+        <v>0.0896757364273071</v>
       </c>
       <c r="O5" t="n">
-        <v>2.053386211395264</v>
+        <v>2.266554117202759</v>
       </c>
       <c r="P5" t="n">
-        <v>2.270004272460937</v>
+        <v>6.198113203048706</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.886881351470948</v>
+        <v>4.483786821365356</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-181131</t>
+          <t>20250731-010845</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="C6" t="n">
-        <v>45.00781750679016</v>
+        <v>126.8786475658417</v>
       </c>
       <c r="D6" t="n">
-        <v>1.679999947547913</v>
+        <v>13.59000015258789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1103586951049707</v>
+        <v>0.237759536949166</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3529411852359772</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3083004057407379</v>
+        <v>0.4651162922382355</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1774193495512008</v>
+        <v>0.2814814746379852</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1860465109348297</v>
+        <v>0.2647058963775635</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08031443506479261</v>
+        <v>0.0922360196709632</v>
       </c>
       <c r="K6" t="n">
-        <v>14.84200596809387</v>
+        <v>29.42365193367004</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0412761402130126</v>
+        <v>0.0417313480377197</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0527160882949829</v>
+        <v>0.1245628023147583</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0573737096786499</v>
+        <v>0.096841230392456</v>
       </c>
       <c r="O6" t="n">
-        <v>2.063807010650635</v>
+        <v>2.086567401885986</v>
       </c>
       <c r="P6" t="n">
-        <v>2.635804414749145</v>
+        <v>6.228140115737915</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.868685483932495</v>
+        <v>4.842061519622803</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-181356</t>
+          <t>20250731-011059</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>47.88446378707886</v>
+        <v>25.69539713859558</v>
       </c>
       <c r="D2" t="n">
-        <v>5.349999904632568</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1003223840380087</v>
+        <v>0.1464085984846641</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2857142984867096</v>
+        <v>0.4545454680919647</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2681564390659332</v>
+        <v>0.3461538553237915</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1417322903871536</v>
+        <v>0.3478260934352875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1417322903871536</v>
+        <v>0.3523316085338592</v>
       </c>
       <c r="J2" t="n">
-        <v>0.103516548871994</v>
+        <v>0.1046586781740188</v>
       </c>
       <c r="K2" t="n">
-        <v>14.03157949447632</v>
+        <v>13.49935221672058</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0512210369110107</v>
+        <v>0.0382686614990234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0481459665298461</v>
+        <v>0.0794192457199096</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0415976476669311</v>
+        <v>0.08376228809356689</v>
       </c>
       <c r="O2" t="n">
-        <v>2.561051845550537</v>
+        <v>1.913433074951172</v>
       </c>
       <c r="P2" t="n">
-        <v>2.40729832649231</v>
+        <v>3.970962285995483</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.079882383346558</v>
+        <v>4.188114404678345</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-074504</t>
+          <t>20250627-153630</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>46.70638179779053</v>
+        <v>44.75134325027466</v>
       </c>
       <c r="D3" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0994015827309339</v>
+        <v>0.1466281441626725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2666666805744171</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2745098173618316</v>
+        <v>0.4188034236431122</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2722513079643249</v>
+        <v>0.270676702260971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2769230902194977</v>
+        <v>0.2835820913314819</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1479525417089462</v>
+        <v>0.1081664115190506</v>
       </c>
       <c r="K3" t="n">
-        <v>14.0804328918457</v>
+        <v>13.43258690834045</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0484239387512207</v>
+        <v>0.0373887300491333</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0475365734100341</v>
+        <v>0.0773399543762207</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0412440919876098</v>
+        <v>0.0860144567489624</v>
       </c>
       <c r="O3" t="n">
-        <v>2.421196937561035</v>
+        <v>1.869436502456665</v>
       </c>
       <c r="P3" t="n">
-        <v>2.376828670501709</v>
+        <v>3.866997718811035</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.062204599380493</v>
+        <v>4.30072283744812</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-074648</t>
+          <t>20250627-153748</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>47.06493401527405</v>
+        <v>25.30725908279419</v>
       </c>
       <c r="D4" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1007654151180758</v>
+        <v>0.1473251129018849</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1926605552434921</v>
+        <v>0.4100418388843536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1926605552434921</v>
+        <v>0.3687150776386261</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1970443278551101</v>
+        <v>0.3387978076934814</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0911419466137886</v>
+        <v>0.0897835716605186</v>
       </c>
       <c r="K4" t="n">
-        <v>14.10280752182007</v>
+        <v>13.56775760650635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0477690076828002</v>
+        <v>0.0392326593399047</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0487841510772705</v>
+        <v>0.0769330167770385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0417043304443359</v>
+        <v>0.0853833246231079</v>
       </c>
       <c r="O4" t="n">
-        <v>2.388450384140014</v>
+        <v>1.96163296699524</v>
       </c>
       <c r="P4" t="n">
-        <v>2.439207553863525</v>
+        <v>3.846650838851929</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.085216522216797</v>
+        <v>4.269166231155396</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-074829</t>
+          <t>20250627-153926</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>30.3015820980072</v>
+        <v>25.28828096389771</v>
       </c>
       <c r="D5" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1020105740962883</v>
+        <v>0.1463801372667838</v>
       </c>
       <c r="F5" t="n">
-        <v>0.190476194024086</v>
+        <v>0.3333333432674408</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1045751646161079</v>
+        <v>0.2309859097003936</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0483870953321456</v>
+        <v>0.1678321659564972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0640000030398368</v>
+        <v>0.1666666716337204</v>
       </c>
       <c r="J5" t="n">
-        <v>0.09942414611577979</v>
+        <v>0.091007225215435</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0344250202179</v>
+        <v>13.36837005615234</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0415468502044677</v>
+        <v>0.0349518728256225</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0484028625488281</v>
+        <v>0.06847220897674559</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0411539602279663</v>
+        <v>0.0865973091125488</v>
       </c>
       <c r="O5" t="n">
-        <v>2.077342510223389</v>
+        <v>1.747593641281128</v>
       </c>
       <c r="P5" t="n">
-        <v>2.420143127441406</v>
+        <v>3.42361044883728</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.057698011398315</v>
+        <v>4.329865455627441</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-075012</t>
+          <t>20250627-154044</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>64.39712429046631</v>
+        <v>29.03203344345093</v>
       </c>
       <c r="D6" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1005019933152734</v>
+        <v>0.1417459674617823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1739130467176437</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3135593235492706</v>
+        <v>0.3138461410999298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2978723347187042</v>
+        <v>0.3020833432674408</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3090128898620605</v>
+        <v>0.3253588378429413</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09288846701383589</v>
+        <v>0.1049238294363021</v>
       </c>
       <c r="K6" t="n">
-        <v>8.534703493118286</v>
+        <v>13.37768578529358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404927396774291</v>
+        <v>0.0351402568817138</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0469771337509155</v>
+        <v>0.06880935192108149</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0425577783584594</v>
+        <v>0.0847022199630737</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02463698387146</v>
+        <v>1.757012844085693</v>
       </c>
       <c r="P6" t="n">
-        <v>2.348856687545776</v>
+        <v>3.440467596054077</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.127888917922974</v>
+        <v>4.235110998153687</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-075137</t>
+          <t>20250627-154206</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>96.54265475273132</v>
+        <v>37.50004315376282</v>
       </c>
       <c r="D2" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1572445161799167</v>
+        <v>0.1050886741402197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2666666805744171</v>
+        <v>0.3076923191547394</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4648648500442505</v>
+        <v>0.2590673565864563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4632768332958221</v>
+        <v>0.2307692319154739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4418604671955108</v>
+        <v>0.2266666740179062</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0698452889919281</v>
+        <v>0.0778075903654098</v>
       </c>
       <c r="K2" t="n">
-        <v>29.69973921775818</v>
+        <v>9.544999361038208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0531968021392822</v>
+        <v>0.0459427833557128</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1237636709213256</v>
+        <v>0.0454104471206665</v>
       </c>
       <c r="N2" t="n">
-        <v>0.091940541267395</v>
+        <v>0.06394800186157221</v>
       </c>
       <c r="O2" t="n">
-        <v>2.659840106964112</v>
+        <v>2.297139167785645</v>
       </c>
       <c r="P2" t="n">
-        <v>6.188183546066284</v>
+        <v>2.270522356033325</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.597027063369751</v>
+        <v>3.197400093078613</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-094531</t>
+          <t>20250701-180616</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>53.99438118934631</v>
+        <v>45.36940288543701</v>
       </c>
       <c r="D3" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1585819859195638</v>
+        <v>0.1101259498272911</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3571428656578064</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4455958604812622</v>
+        <v>0.4248704612255096</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4299065470695495</v>
+        <v>0.4304932653903961</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4334975481033325</v>
+        <v>0.4266666769981384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07621577382087701</v>
+        <v>0.08363133668899531</v>
       </c>
       <c r="K3" t="n">
-        <v>29.71704983711243</v>
+        <v>14.80393075942993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0550925636291503</v>
+        <v>0.0426624345779418</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1321520948410034</v>
+        <v>0.0521679925918579</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0913870429992675</v>
+        <v>0.0575768184661865</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75462818145752</v>
+        <v>2.133121728897095</v>
       </c>
       <c r="P3" t="n">
-        <v>6.607604742050171</v>
+        <v>2.608399629592896</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.569352149963379</v>
+        <v>2.878840923309326</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-094835</t>
+          <t>20250701-180752</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>47.201500415802</v>
+        <v>58.21130180358887</v>
       </c>
       <c r="D4" t="n">
-        <v>7.46999979019165</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1582911674949255</v>
+        <v>0.107912309845037</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.2580645084381103</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3076923191547394</v>
+        <v>0.125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3212435245513916</v>
+        <v>0.0625</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3058823645114898</v>
+        <v>0.0495867766439914</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07398206740617751</v>
+        <v>0.0871911346912384</v>
       </c>
       <c r="K4" t="n">
-        <v>29.85367155075073</v>
+        <v>14.84439039230347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0541330814361572</v>
+        <v>0.0400602912902832</v>
       </c>
       <c r="M4" t="n">
-        <v>0.135489273071289</v>
+        <v>0.0508607530593872</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0909598112106323</v>
+        <v>0.0569802618026733</v>
       </c>
       <c r="O4" t="n">
-        <v>2.706654071807861</v>
+        <v>2.00301456451416</v>
       </c>
       <c r="P4" t="n">
-        <v>6.774463653564453</v>
+        <v>2.54303765296936</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.547990560531616</v>
+        <v>2.849013090133667</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-095056</t>
+          <t>20250701-180935</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="C5" t="n">
-        <v>46.91525888442993</v>
+        <v>87.24979496002197</v>
       </c>
       <c r="D5" t="n">
-        <v>7.440000057220459</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1577158776873891</v>
+        <v>0.1108011788054674</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3478260934352875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3578947484493255</v>
+        <v>0.4266666769981384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3037974536418915</v>
+        <v>0.427807480096817</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2631579041481018</v>
+        <v>0.4153005480766296</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08960624039173121</v>
+        <v>0.0707604438066482</v>
       </c>
       <c r="K5" t="n">
-        <v>24.03130960464477</v>
+        <v>15.15977478027344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06451964855194089</v>
+        <v>0.0410677242279052</v>
       </c>
       <c r="M5" t="n">
-        <v>0.124301962852478</v>
+        <v>0.0454000854492187</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0912265586853027</v>
+        <v>0.0577376270294189</v>
       </c>
       <c r="O5" t="n">
-        <v>3.225982427597046</v>
+        <v>2.053386211395264</v>
       </c>
       <c r="P5" t="n">
-        <v>6.215098142623901</v>
+        <v>2.270004272460937</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.561327934265137</v>
+        <v>2.886881351470948</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-095311</t>
+          <t>20250701-181131</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>49.50776147842407</v>
+        <v>45.00781750679016</v>
       </c>
       <c r="D6" t="n">
-        <v>7.449999809265137</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1568399363634537</v>
+        <v>0.1103586951049707</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2857142984867096</v>
+        <v>0.3529411852359772</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2456140369176864</v>
+        <v>0.3083004057407379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2604166567325592</v>
+        <v>0.1774193495512008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2758620679378509</v>
+        <v>0.1860465109348297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0824107527732849</v>
+        <v>0.08031443506479261</v>
       </c>
       <c r="K6" t="n">
-        <v>29.64809036254883</v>
+        <v>14.84200596809387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0611167955398559</v>
+        <v>0.0412761402130126</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1309273719787597</v>
+        <v>0.0527160882949829</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0902737712860107</v>
+        <v>0.0573737096786499</v>
       </c>
       <c r="O6" t="n">
-        <v>3.055839776992798</v>
+        <v>2.063807010650635</v>
       </c>
       <c r="P6" t="n">
-        <v>6.546368598937988</v>
+        <v>2.635804414749145</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.513688564300537</v>
+        <v>2.868685483932495</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-095525</t>
+          <t>20250701-181356</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
